--- a/r5-core-50-Gemeindekennziffer/StructureDefinition-at-core-address.xlsx
+++ b/r5-core-50-Gemeindekennziffer/StructureDefinition-at-core-address.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://hl7.at/fhir/HL7ATCoreProfiles/5.0.0/StructureDefinition/at-core-address</t>
+    <t>https://fhir.hl7.at/core/r5/StructureDefinition/at-core-address</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-07T12:16:57+00:00</t>
+    <t>2026-10-13T08:41:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -348,14 +348,14 @@
     <t>municipalityCode</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://hl7.at/fhir/HL7ATCoreProfiles/5.0.0/StructureDefinition/at-core-ext-address-municipalityCode}
+    <t xml:space="preserve">Extension {https://fhir.hl7.at/core/r5/StructureDefinition/at-core-ext-address-municipalityCode}
 </t>
   </si>
   <si>
-    <t>Address Municipality Code</t>
-  </si>
-  <si>
-    <t>HL7® Austria FHIR® Core Extension for the municipality code part of the Austrian address</t>
+    <t>Address Municipality Code (Gemeindecode)</t>
+  </si>
+  <si>
+    <t>HL7® Austria FHIR® Core Extension for the municipality code (Gemeindecode) part of the Austrian address. The municipality code is related to the [municipality key (Gemeindekennziffer)](StructureDefinition-at-core-ext-address-municipalityKey.html). While these two are generally identical, there is one notable exception: in Vienna, the municipality key (Gemeindekennziffer) is consistently 90001, whereas the municipality code (Gemeindecode) varies by district. The current list of values is provided by [Statistik Austria](https://www.statistik.at/verzeichnis/reglisten/gemliste_knz.pdf).</t>
   </si>
   <si>
     <t>Address.extension:municipalityKey</t>
@@ -364,14 +364,14 @@
     <t>municipalityKey</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://hl7.at/fhir/HL7ATCoreProfiles/5.0.0/StructureDefinition/at-core-ext-address-municipalityKey}
+    <t xml:space="preserve">Extension {https://fhir.hl7.at/core/r5/StructureDefinition/at-core-ext-address-municipalityKey}
 </t>
   </si>
   <si>
-    <t>Address Municipality Key</t>
-  </si>
-  <si>
-    <t>HL7® Austria FHIR® Core Extension for the municipality key part of the Austrian address</t>
+    <t>Address Municipality Key (Gemeindekennziffer)</t>
+  </si>
+  <si>
+    <t>HL7® Austria FHIR® Core Extension for the municipality key (Gemeindekennziffer) part of the Austrian address. The municipality key is related to the [municipality code (Gemeindecode)](StructureDefinition-at-core-ext-address-municipalityCode.html). While these two are generally identical, there is one notable exception: in Vienna, the municipality key (Gemeindekennziffer) is consistently 90001, whereas the municipality code (Gemeindecode) varies by district. The current list of values is provided by [Statistik Austria](https://www.statistik.at/verzeichnis/reglisten/gemliste_knz.pdf).</t>
   </si>
   <si>
     <t>Address.use</t>
@@ -578,7 +578,7 @@
     <t>additionalInformation</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://hl7.at/fhir/HL7ATCoreProfiles/5.0.0/StructureDefinition/at-core-ext-address-additionalInformation}
+    <t xml:space="preserve">Extension {https://fhir.hl7.at/core/r5/StructureDefinition/at-core-ext-address-additionalInformation}
 </t>
   </si>
   <si>
@@ -1084,7 +1084,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="92.1484375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="79.4921875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
